--- a/SourceData/Datas/craft_cost.xlsx
+++ b/SourceData/Datas/craft_cost.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1320,6 +1320,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>can_basic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>can_basic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dirt</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>axe_basic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>axe_basic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>grass</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rod_basic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rod_basic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>grass</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SourceData/Datas/craft_cost.xlsx
+++ b/SourceData/Datas/craft_cost.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="18400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="craft_cost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="craft_cost" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1178,16 +1178,16 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>seed_mix</t>
+          <t>can_basic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dirt</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1196,34 +1196,34 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>can_basic</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dirt</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>seed_mix</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>grass</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wood_bundle</t>
+          <t>axe_basic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1232,11 +1232,11 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wood_bundle</t>
+          <t>axe_basic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1245,186 +1245,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>stone_pack</t>
+          <t>rod_basic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stone</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>stone_pack</t>
+          <t>rod_basic</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>dirt</t>
+          <t>grass</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fish_bait_seed</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>fish_bait_seed</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>grass</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>can_basic</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>stone</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>can_basic</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>dirt</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>axe_basic</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>stone</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>axe_basic</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>grass</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rod_basic</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>wood</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rod_basic</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>grass</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
         <v>2</v>
       </c>
     </row>
